--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DDV_HRM-2031-0100/Panel-28/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DDV_HRM-2031-0100/Panel-28/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
@@ -463,10 +463,10 @@
         <v>16.71965</v>
       </c>
       <c r="D2" t="n">
+        <v>16.40401</v>
+      </c>
+      <c r="E2" t="n">
         <v>16.63617</v>
-      </c>
-      <c r="E2" t="n">
-        <v>16.40401</v>
       </c>
       <c r="F2" t="n">
         <v>42.66506</v>
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.57614</v>
+        <v>16.94625</v>
       </c>
       <c r="D3" t="n">
         <v>16.392</v>
       </c>
       <c r="E3" t="n">
-        <v>16.94625</v>
+        <v>16.57614</v>
       </c>
       <c r="F3" t="n">
         <v>42.77248</v>
@@ -510,13 +510,13 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>16.78039</v>
+      </c>
+      <c r="D4" t="n">
+        <v>16.36385</v>
+      </c>
+      <c r="E4" t="n">
         <v>16.50077</v>
-      </c>
-      <c r="D4" t="n">
-        <v>16.78039</v>
-      </c>
-      <c r="E4" t="n">
-        <v>16.36385</v>
       </c>
       <c r="F4" t="n">
         <v>41.95737</v>
